--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="651">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -708,7 +708,13 @@
     <t>241</t>
   </si>
   <si>
-    <t>Foyer d'Action Educative (F.A.E.)</t>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d'Activité de Jour</t>
   </si>
   <si>
     <t>246</t>
@@ -1449,12 +1455,6 @@
     <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
   </si>
   <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
-  </si>
-  <si>
     <t>419</t>
   </si>
   <si>
@@ -1497,12 +1497,6 @@
     <t>Syndicat Inter Hospitalier (S.I.H.)</t>
   </si>
   <si>
-    <t>427</t>
-  </si>
-  <si>
-    <t>Service Educatif Auprès des Tribunaux (S.E.A.T.)</t>
-  </si>
-  <si>
     <t>430</t>
   </si>
   <si>
@@ -1566,13 +1560,13 @@
     <t>440</t>
   </si>
   <si>
-    <t>Service Investigation Orientation Educative (S.I.O.E.)</t>
+    <t>Service d'Investigation Educative</t>
   </si>
   <si>
     <t>441</t>
   </si>
   <si>
-    <t>Centre d'Action Educative (C.A.E.)</t>
+    <t>Service d'Intervention Educative en Milieu Ouvert</t>
   </si>
   <si>
     <t>442</t>
@@ -1641,12 +1635,6 @@
     <t>Régie de Quartier</t>
   </si>
   <si>
-    <t>453</t>
-  </si>
-  <si>
-    <t>Service de Réparation Pénale</t>
-  </si>
-  <si>
     <t>460</t>
   </si>
   <si>
@@ -1662,7 +1650,7 @@
     <t>462</t>
   </si>
   <si>
-    <t>Lieux de vie</t>
+    <t>Lieux de Vie et d'Accueil</t>
   </si>
   <si>
     <t>463</t>
@@ -1926,13 +1914,19 @@
     <t>646</t>
   </si>
   <si>
-    <t>Centre de Vaccination International</t>
+    <t>Centre de Vaccination Internationale</t>
   </si>
   <si>
     <t>647</t>
   </si>
   <si>
     <t>Equipe de Soins Spécialisés</t>
+  </si>
+  <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>Structure qui contribue au Service d'Accès aux Soins</t>
   </si>
   <si>
     <t>695</t>
@@ -2241,7 +2235,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B313"/>
+  <dimension ref="A1:B312"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4733,23 +4727,15 @@
         <v>648</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>650</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="B313" t="s" s="2">
-        <v>652</v>
       </c>
     </row>
   </sheetData>
